--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251202_201433.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251202_201433.xlsx
@@ -4624,7 +4624,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4798,7 +4798,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4856,7 +4856,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251202_201433.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251202_201433.xlsx
@@ -4624,7 +4624,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4798,7 +4798,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4856,7 +4856,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6364,7 +6364,7 @@
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6538,7 +6538,7 @@
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6596,7 +6596,7 @@
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6828,7 +6828,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251202_201433.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251202_201433.xlsx
@@ -6306,7 +6306,7 @@
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -6654,7 +6654,7 @@
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -6712,7 +6712,7 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251202_201433.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251202_201433.xlsx
@@ -6364,7 +6364,7 @@
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6538,7 +6538,7 @@
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6596,7 +6596,7 @@
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6828,7 +6828,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251202_201433.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251202_201433.xlsx
@@ -6306,7 +6306,7 @@
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -6654,7 +6654,7 @@
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -6712,7 +6712,7 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251202_201433.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251202_201433.xlsx
@@ -6306,7 +6306,7 @@
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -6364,7 +6364,7 @@
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6538,7 +6538,7 @@
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6596,7 +6596,7 @@
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6654,7 +6654,7 @@
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -6712,7 +6712,7 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -6828,7 +6828,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251202_201433.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251202_201433.xlsx
@@ -6306,7 +6306,7 @@
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -6364,7 +6364,7 @@
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6538,7 +6538,7 @@
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6596,7 +6596,7 @@
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6654,7 +6654,7 @@
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -6712,7 +6712,7 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -6828,7 +6828,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251202_201433.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251202_201433.xlsx
@@ -4624,7 +4624,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4798,7 +4798,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4856,7 +4856,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251202_201433.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251202_201433.xlsx
@@ -4624,7 +4624,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4798,7 +4798,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4856,7 +4856,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6306,7 +6306,7 @@
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -6654,7 +6654,7 @@
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -6712,7 +6712,7 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251202_201433.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251202_201433.xlsx
@@ -6364,7 +6364,7 @@
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6538,7 +6538,7 @@
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6596,7 +6596,7 @@
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6828,7 +6828,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251202_201433.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251202_201433.xlsx
@@ -4624,7 +4624,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4798,7 +4798,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4856,7 +4856,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6364,7 +6364,7 @@
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6538,7 +6538,7 @@
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6596,7 +6596,7 @@
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6828,7 +6828,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251202_201433.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251202_201433.xlsx
@@ -4624,7 +4624,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4798,7 +4798,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4856,7 +4856,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6306,7 +6306,7 @@
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -6364,7 +6364,7 @@
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6538,7 +6538,7 @@
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6596,7 +6596,7 @@
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6654,7 +6654,7 @@
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -6712,7 +6712,7 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -6828,7 +6828,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251202_201433.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251202_201433.xlsx
@@ -6306,7 +6306,7 @@
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -6364,7 +6364,7 @@
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6538,7 +6538,7 @@
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6596,7 +6596,7 @@
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6654,7 +6654,7 @@
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -6712,7 +6712,7 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -6828,7 +6828,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251202_201433.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251202_201433.xlsx
@@ -4624,7 +4624,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4798,7 +4798,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4856,7 +4856,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6364,7 +6364,7 @@
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6538,7 +6538,7 @@
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6596,7 +6596,7 @@
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6828,7 +6828,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
